--- a/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Esteban est à la cuisine. Il a soif. Sa bouche est sèche. Maman pose un verre. Dedans, il y a de l'eau. Esteban prend le verre. Il boit. L'eau est fraîche. Maman dit : quand on a soif, on boit de l'eau dans un verre. Esteban repose le verre. Il dit : j'avais soif. Merci l'eau.</t>
+          <t>Esteban est à la cuisine. Il a soif. Sa bouche est sèche. Maman pose un verre. Dedans, il y a de l'eau. Esteban prend le verre. Il boit. L'eau est fraîche. Quand on a soif, on boit de l'eau dans un verre. Esteban repose le verre. J'avais soif. Merci l'eau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Esteban est à la cuisine. Il a soif. Sa bouche est sèche. Maman pose un verre. Dedans, il y a de l'eau. Esteban prend le verre. Il boit. L'eau est fraîche.
+maman|Quand on a soif, on boit de l'eau dans un verre.
+narrateur|Esteban repose le verre.
+narrateur|J'avais soif. Merci l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Esteban a soif. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Esteban a eu soif. Il a pris le verre d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman essuie la table. Esteban sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|J'avais soif. Merci l'eau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Esteban a soif. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Esteban a eu soif. Il a pris le verre d'eau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Maman essuie la table. Esteban sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Esteban boit de l'eau</t>
+          <t>Les gouttes sur la carafe</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les chaussures sèchent. La carafe sue des gouttes. Amir rentre, la bouche sèche. Il s'assoit. Il boit l'eau du verre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Esteban est à la cuisine. Il a soif. Sa bouche est sèche. Maman pose un verre. Dedans, il y a de l'eau. Esteban prend le verre. Il boit. L'eau est fraîche. Quand on a soif, on boit de l'eau dans un verre. Esteban repose le verre. J'avais soif. Merci l'eau.</t>
+          <t>Les chaussures sèchent près de la porte. Un peu de terre reste collée. Le frigo fait un petit ronron. Sur la table, une carafe attend. Des gouttes glissent sur le verre. Amir vit ici, avec maman. Papa est au jardin, tout près. Dehors, le soleil tape encore. Amir rentre du jeu. Ses joues sont chaudes. Sa bouche est sèche. Maman, j'ai soif. Tu as chaud, Amir ? Oui. Ma bouche est sèche. Viens. Il y a de l'eau. Amir marche vers la cuisine. Le carrelage est un peu froid. Ça fait du bien aux pieds. Assieds-toi un moment. Amir tire sa chaise. Il s'assoit près de la table. Il pose les mains à plat. Bravo, Amir. Tu es bien assis. Maman prend la carafe. Les gouttes brillent au soleil. On dirait des perles ! Oui. Des perles d'eau. Tu as bien regardé. Maman verse dans un verre. L'eau fait un petit chant. Le verre se remplit. Tu prends le verre ? Amir prend le verre. Il le tient à deux mains. Il boit une gorgée. L'eau est fraîche. C'est froid, maman. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo, Amir. Amir boit encore une gorgée. Puis une autre. Il repose le verre. Merci l'eau. Merci maman. Tu as bien bu. C'est du bon travail. Un oiseau passe devant la fenêtre. Tu l'as vu, l'oiseau ? Oui. Il va vite.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1329,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Esteban est à la cuisine. Il a soif. Sa bouche est sèche. Maman pose un verre. Dedans, il y a de l'eau. Esteban prend le verre. Il boit. L'eau est fraîche.
-maman|Quand on a soif, on boit de l'eau dans un verre.
-narrateur|Esteban repose le verre.
-narrateur|J'avais soif. Merci l'eau.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les chaussures sèchent près de la porte.
+narrateur|Un peu de terre reste collée.
+narrateur|Le frigo fait un petit ronron.
+narrateur|Sur la table, une carafe attend.
+narrateur|Des gouttes glissent sur le verre.
+narrateur|Amir vit ici, avec maman.
+narrateur|Papa est au jardin, tout près.
+narrateur|Dehors, le soleil tape encore.
+narrateur|Amir rentre du jeu.
+narrateur|Ses joues sont chaudes.
+narrateur|Sa bouche est sèche.
+enfant-m|Maman, j'ai soif.
+maman|Tu as chaud, Amir ?
+enfant-m|Oui.
+enfant-m|Ma bouche est sèche.
+maman|Viens.
+maman|Il y a de l'eau.
+narrateur|Amir marche vers la cuisine.
+narrateur|Le carrelage est un peu froid.
+narrateur|Ça fait du bien aux pieds.
+maman|Assieds-toi un moment.
+narrateur|Amir tire sa chaise.
+narrateur|Il s'assoit près de la table.
+narrateur|Il pose les mains à plat.
+maman|Bravo, Amir.
+maman|Tu es bien assis.
+narrateur|Maman prend la carafe.
+narrateur|Les gouttes brillent au soleil.
+enfant-m|On dirait des perles !
+maman|Oui.
+maman|Des perles d'eau.
+maman|Tu as bien regardé.
+narrateur|Maman verse dans un verre.
+narrateur|L'eau fait un petit chant.
+narrateur|Le verre se remplit.
+maman|Tu prends le verre ?
+narrateur|Amir prend le verre.
+narrateur|Il le tient à deux mains.
+narrateur|Il boit une gorgée.
+narrateur|L'eau est fraîche.
+enfant-m|C'est froid, maman.
+maman|Oui.
+maman|Quand on a soif, on boit de l'eau.
+maman|On boit dans un verre.
+maman|Bravo, Amir.
+narrateur|Amir boit encore une gorgée.
+narrateur|Puis une autre.
+narrateur|Il repose le verre.
+enfant-m|Merci l'eau.
+enfant-m|Merci maman.
+maman|Tu as bien bu.
+maman|C'est du bon travail.
+narrateur|Un oiseau passe devant la fenêtre.
+maman|Tu l'as vu, l'oiseau ?
+enfant-m|Oui.
+enfant-m|Il va vite.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>carafe,verre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Esteban a soif. Que fait-il ?</t>
+          <t>Amir a soif. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Esteban a soif. Que fait-il ?</t>
+          <t>narrateur|Amir a soif.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Esteban a eu soif. Il a pris le verre d'eau.</t>
+          <t>Amir a eu soif. Il a pris le verre d'eau. Il a bu. Tu as pris le verre ? Oui. J'ai bu de l'eau. Bravo, Amir. Quand on a soif, on boit de l'eau. Le verre reste près de la carafe. Tu te sens mieux ? Oui. Ma bouche n'est plus sèche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,7 +1749,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Esteban a eu soif. Il a pris le verre d'eau.</t>
+          <t>narrateur|Amir a eu soif.
+narrateur|Il a pris le verre d'eau.
+narrateur|Il a bu.
+maman|Tu as pris le verre ?
+enfant-m|Oui.
+enfant-m|J'ai bu de l'eau.
+maman|Bravo, Amir.
+maman|Quand on a soif, on boit de l'eau.
+narrateur|Le verre reste près de la carafe.
+maman|Tu te sens mieux ?
+enfant-m|Oui.
+enfant-m|Ma bouche n'est plus sèche.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1703,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman essuie la table. Esteban sourit.</t>
+          <t>Maman essuie une goutte sur la table. Amir reste assis. Encore une petite gorgée ? Amir reprend le verre. Il boit une dernière gorgée. Il repose le verre. C'était frais. Oui. L'eau, c'est bien quand on a soif. Merci, maman. Merci, Amir. On reste encore un peu ensemble ? Oui. Le frigo ronronne encore. Les chaussures sèchent près de la porte. Tu as fait du bon travail. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1924,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman essuie la table. Esteban sourit.</t>
+          <t>narrateur|Maman essuie une goutte sur la table.
+narrateur|Amir reste assis.
+maman|Encore une petite gorgée ?
+narrateur|Amir reprend le verre.
+narrateur|Il boit une dernière gorgée.
+narrateur|Il repose le verre.
+enfant-m|C'était frais.
+maman|Oui.
+maman|L'eau, c'est bien quand on a soif.
+enfant-m|Merci, maman.
+maman|Merci, Amir.
+maman|On reste encore un peu ensemble ?
+enfant-m|Oui.
+narrateur|Le frigo ronronne encore.
+narrateur|Les chaussures sèchent près de la porte.
+maman|Tu as fait du bon travail.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1968,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2108,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'avais soif.
+enfant-m|J'ai pris le verre.
+enfant-m|J'ai bu de l'eau.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures sèchent près de la porte. Un peu de terre reste collée. Le frigo fait un petit ronron. Sur la table, une carafe attend. Des gouttes glissent sur le verre. Amir vit ici, avec maman. Papa est au jardin, tout près. Dehors, le soleil tape encore. Amir rentre du jeu. Ses joues sont chaudes. Sa bouche est sèche. Maman, j'ai soif. Tu as chaud, Amir ? Oui. Ma bouche est sèche. Viens. Il y a de l'eau. Amir marche vers la cuisine. Le carrelage est un peu froid. Ça fait du bien aux pieds. Assieds-toi un moment. Amir tire sa chaise. Il s'assoit près de la table. Il pose les mains à plat. Bravo, Amir. Tu es bien assis. Maman prend la carafe. Les gouttes brillent au soleil. On dirait des perles ! Oui. Des perles d'eau. Tu as bien regardé. Maman verse dans un verre. L'eau fait un petit chant. Le verre se remplit. Tu prends le verre ? Amir prend le verre. Il le tient à deux mains. Il boit une gorgée. L'eau est fraîche. C'est froid, maman. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo, Amir. Amir boit encore une gorgée. Puis une autre. Il repose le verre. Merci l'eau. Merci maman. Tu as bien bu. C'est du bon travail. Un oiseau passe devant la fenêtre. Tu l'as vu, l'oiseau ? Oui. Il va vite.</t>
+          <t>Les chaussures sèchent près de la porte. Un peu de terre reste collée. Le frigo fait un petit ronron. Sur la table, une carafe attend. Des gouttes glissent sur le verre. Amir vit ici, avec maman. Papa est au jardin, tout près. Dehors, le soleil tape encore. Amir rentre du jeu. Ses joues sont chaudes. Sa bouche est sèche. Maman, j'ai soif. Tu as chaud, Amir ? Oui. Ma bouche est sèche. Viens. Il y a de l'eau. Amir marche vers la cuisine. Le carrelage est un peu froid. Ça fait du bien aux pieds. Assieds-toi un moment. Amir tire sa chaise. Il s'assoit près de la table. Il pose les mains à plat. Bravo, Amir. Tu es bien assis. Maman prend la carafe. Les gouttes brillent au soleil. On dirait des perles ! Oui. Des perles d'eau. Tu as bien regardé. Maman verse dans un verre. L'eau fait un petit chant. Le verre se remplit. Tu prends le verre ? Amir prend le verre. Il le tient à deux mains. Il boit une gorgée. L'eau est fraîche. C'est froid, maman. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo, Amir. Amir boit encore une gorgée. Puis une autre. Il repose le verre. Merci l'eau. Merci maman. Tu as bien bu. Un oiseau passe devant la fenêtre. Tu l'as vu, l'oiseau ? Oui. Il va vite.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Esteban est à la cuisine. Il a soif. Sa bouche est sèche. Maman pose un verre. Dedans, il y a de l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Esteban prend le verre. Il boit. L'eau est fraîche. Maman dit : quand on a soif, on boit de l'eau dans un verre. Esteban repose le verre. Il dit : j'avais soif. Merci l'eau.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussures sèchent près de la porte. Un peu de terre reste collée. Le frigo fait un petit ronron. Sur la table, une carafe attend. Des gouttes glissent sur le verre. Amir vit ici, avec maman. Papa est au jardin, tout près. Dehors, le soleil tape encore. Amir rentre du jeu. Ses joues sont chaudes. Sa bouche est sèche. Maman, j'ai soif. Tu as chaud, Amir ? Oui. Ma bouche est sèche. Viens. Il y a de l'eau. Amir marche vers la cuisine. Le carrelage est un peu froid. Ça fait du bien aux pieds. Assieds-toi un moment. Amir tire sa chaise. Il s'assoit près de la table. Il pose les mains à plat. Bravo, Amir. Tu es bien assis. Maman prend la carafe. Les gouttes brillent au soleil. On dirait des perles ! Oui. Des perles d'eau. Tu as bien regardé. Maman verse dans un verre. L'eau fait un petit chant. Le verre se remplit. Tu prends le verre ? Amir prend le verre. Il le tient à deux mains. Il boit une gorgée. L'eau est fraîche. C'est froid, maman. Oui. Quand on a soif, on boit de l'eau. On boit dans un verre. Bravo, Amir. Amir boit encore une gorgée. Puis une autre. Il repose le verre. Merci l'eau. Merci maman. Tu as bien bu. Un oiseau passe devant la fenêtre. Tu l'as vu, l'oiseau ? Oui. Il va vite.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 enfant-m|Merci l'eau.
 enfant-m|Merci maman.
 maman|Tu as bien bu.
-maman|C'est du bon travail.
 narrateur|Un oiseau passe devant la fenêtre.
 maman|Tu l'as vu, l'oiseau ?
 enfant-m|Oui.
@@ -1421,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Esteban a &lt;emphasis level="moderate"&gt;soif&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a soif. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1579,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1610,7 +1608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Esteban a eu soif. Il a pris le verre d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a eu soif. Il a pris le verre d'eau. Il a bu. Tu as pris le verre ? Oui. J'ai bu de l'eau. Bravo, Amir. Quand on a soif, on boit de l'eau. Le verre reste près de la carafe. Tu te sens mieux ? Oui. Ma bouche n'est plus sèche.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1763,7 +1761,6 @@
 enfant-m|Ma bouche n'est plus sèche.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,12 +1785,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman essuie une goutte sur la table. Amir reste assis. Encore une petite gorgée ? Amir reprend le verre. Il boit une dernière gorgée. Il repose le verre. C'était frais. Oui. L'eau, c'est bien quand on a soif. Merci, maman. Merci, Amir. On reste encore un peu ensemble ? Oui. Le frigo ronronne encore. Les chaussures sèchent près de la porte. Tu as fait du bon travail. Bravo.</t>
+          <t>Maman essuie une goutte sur la table. Amir reste assis. Encore une petite gorgée ? Amir reprend le verre. Il boit une dernière gorgée. Il repose le verre. C'était frais. Oui. L'eau, c'est bien quand on a soif. Merci, maman. Merci, Amir. On reste encore un peu ensemble ? Oui. Le frigo ronronne encore. Les chaussures sèchent près de la porte. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman essuie la table. Esteban sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman essuie une goutte sur la table. Amir reste assis. Encore une petite gorgée ? Amir reprend le verre. Il boit une dernière gorgée. Il repose le verre. C'était frais. Oui. L'eau, c'est bien quand on a soif. Merci, maman. Merci, Amir. On reste encore un peu ensemble ? Oui. Le frigo ronronne encore. Les chaussures sèchent près de la porte. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,11 +1936,9 @@
 enfant-m|Oui.
 narrateur|Le frigo ronronne encore.
 narrateur|Les chaussures sèchent près de la porte.
-maman|Tu as fait du bon travail.
 maman|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1968,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais soif. J'ai pris le verre. J'ai bu de l'eau. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,12 +2106,9 @@
           <t>enfant-m|J'avais soif.
 enfant-m|J'ai pris le verre.
 enfant-m|J'ai bu de l'eau.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.003-06.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Esteban, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
